--- a/docs/lem/files/xslope_method_slices_problem2.xlsx
+++ b/docs/lem/files/xslope_method_slices_problem2.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
   <si>
     <t>X</t>
   </si>
@@ -630,6 +630,37 @@
   </si>
   <si>
     <t>soil 3</t>
+  </si>
+  <si>
+    <t>psi</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>psi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -8006,7 +8037,7 @@
         <v>79</v>
       </c>
       <c r="D5" s="35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -9451,8 +9482,8 @@
       <c r="I8" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="26" t="s">
-        <v>81</v>
+      <c r="J8" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="K8" s="21" t="s">
         <v>88</v>
@@ -9473,7 +9504,7 @@
         <v>82</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="R8" s="25" t="s">
         <v>92</v>
@@ -10235,7 +10266,7 @@
     <mergeCell ref="W7:X7"/>
     <mergeCell ref="R7:V7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:F50">
+  <conditionalFormatting sqref="F9:F50">
     <cfRule type="expression" dxfId="8" priority="3">
       <formula>$D9="cp"</formula>
     </cfRule>
@@ -10250,7 +10281,7 @@
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M9:N50">
+  <conditionalFormatting sqref="N9:N50">
     <cfRule type="expression" dxfId="5" priority="6">
       <formula>$D9="cp"</formula>
     </cfRule>

--- a/docs/lem/files/xslope_method_slices_problem2.xlsx
+++ b/docs/lem/files/xslope_method_slices_problem2.xlsx
@@ -2641,7 +2641,26 @@
       </c>
       <c r="H2" s="40" t="inlineStr">
         <is>
-          <t>qp</t>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>q</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>p</t>
+          </r>
         </is>
       </c>
       <c r="I2" s="40" t="inlineStr">
@@ -5351,7 +5370,23 @@
       </c>
       <c r="D10" s="48" t="inlineStr">
         <is>
-          <t>gsat</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>g</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+            </rPr>
+            <t>sat</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="44" t="inlineStr">
@@ -5466,12 +5501,64 @@
       </c>
       <c r="AA10" s="46" t="inlineStr">
         <is>
-          <t>s(g)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>g</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>)</t>
+          </r>
         </is>
       </c>
       <c r="AB10" s="46" t="inlineStr">
         <is>
-          <t>s(c)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(c)</t>
+          </r>
         </is>
       </c>
       <c r="AC10" s="47" t="inlineStr">
@@ -5481,17 +5568,70 @@
       </c>
       <c r="AD10" s="46" t="inlineStr">
         <is>
-          <t>s(c/p)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(c/p)</t>
+          </r>
         </is>
       </c>
       <c r="AE10" s="46" t="inlineStr">
         <is>
-          <t>s(d)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(d)</t>
+          </r>
         </is>
       </c>
       <c r="AF10" s="47" t="inlineStr">
         <is>
-          <t>s(psi)</t>
+          <r>
+            <t>s(</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+            </rPr>
+            <t>psi</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>)</t>
+          </r>
         </is>
       </c>
       <c r="AG10" s="23" t="inlineStr">
